--- a/_site/files/재무제표 체크리스트_샘플.xlsx
+++ b/_site/files/재무제표 체크리스트_샘플.xlsx
@@ -1466,6 +1466,45 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1483,45 +1522,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1829,7 +1829,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1843,18 +1843,18 @@
     <col min="1" max="1" width="44.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="15.58203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="57.5" style="5" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="21"/>
+    <col min="4" max="4" width="42.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="15"/>
     <col min="6" max="6" width="23.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="44.25" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="19" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       <c r="C2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="19" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
       <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="16" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1899,10 +1899,10 @@
       <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="16" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1916,14 +1916,14 @@
       <c r="C5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="51">
+    <row r="6" spans="1:7" ht="34">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1933,10 +1933,10 @@
       <c r="C6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="17">
         <v>9.5799999999999996E-2</v>
       </c>
     </row>
@@ -1950,10 +1950,10 @@
       <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1967,10 +1967,10 @@
       <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="15">
         <v>330</v>
       </c>
     </row>
@@ -1978,11 +1978,11 @@
       <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="27">
         <f>SUM(B3:B8)</f>
         <v>60</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="27"/>
     </row>
     <row r="10" spans="1:7" ht="24.75" customHeight="1">
       <c r="A10" s="1" t="s">
@@ -2005,10 +2005,10 @@
       <c r="C11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F11" t="s">
@@ -2025,13 +2025,13 @@
       <c r="C12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="15">
         <v>4.1500000000000004</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="21">
         <v>4.1500000000000004</v>
       </c>
       <c r="G12" t="s">
@@ -2048,13 +2048,13 @@
       <c r="C13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="15">
         <v>3.09</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="21">
         <v>3.09</v>
       </c>
       <c r="G13" t="s">
@@ -2071,16 +2071,16 @@
       <c r="C14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="13" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2088,11 +2088,11 @@
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="27">
         <f>SUM(B11:B14)</f>
         <v>40</v>
       </c>
-      <c r="C15" s="14"/>
+      <c r="C15" s="27"/>
     </row>
     <row r="16" spans="1:7" ht="34">
       <c r="A16" s="1" t="s">
@@ -2104,11 +2104,11 @@
       <c r="C16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="85">
+    <row r="17" spans="1:6" ht="68">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -2118,13 +2118,13 @@
       <c r="C17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="13" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2138,10 +2138,10 @@
       <c r="C18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="15">
         <v>53.2</v>
       </c>
     </row>
@@ -2149,13 +2149,13 @@
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="29">
         <v>10</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="25" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="17"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="7" t="s">
         <v>33</v>
       </c>
@@ -2172,7 +2172,7 @@
       <c r="A21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="18"/>
+      <c r="B21" s="31"/>
       <c r="C21" s="11" t="s">
         <v>36</v>
       </c>
@@ -2181,22 +2181,22 @@
       <c r="A22" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="27">
         <f>SUM(B17:B21)</f>
         <v>30</v>
       </c>
-      <c r="C22" s="14"/>
+      <c r="C22" s="27"/>
     </row>
     <row r="23" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="24" spans="1:6" ht="43.5" customHeight="1">
       <c r="A24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="28">
         <f>(B9+B15+B22)/130*100</f>
         <v>100</v>
       </c>
-      <c r="C24" s="15"/>
+      <c r="C24" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2222,154 +2222,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="28"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" ht="17.5" thickBot="1">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22">
         <v>2018</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28">
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22">
         <v>2021</v>
       </c>
-      <c r="H3" s="28"/>
+      <c r="H3" s="22"/>
     </row>
     <row r="4" spans="1:8" ht="17.5" thickBot="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="23">
         <v>1158.8</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="23">
         <v>1362.5</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="23">
         <v>2380.1</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="23">
         <v>3105.9</v>
       </c>
-      <c r="H4" s="28"/>
+      <c r="H4" s="22"/>
     </row>
     <row r="5" spans="1:8" ht="17.5" thickBot="1">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="24">
         <v>215</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="24">
         <v>269.60000000000002</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="24">
         <v>598.1</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="24">
         <v>659</v>
       </c>
-      <c r="H5" s="28"/>
+      <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" ht="102">
       <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="14">
         <f>D5/D4</f>
         <v>0.18553676216775977</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="14">
         <f t="shared" ref="E6:G6" si="0">E5/E4</f>
         <v>0.19787155963302755</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="14">
         <f t="shared" si="0"/>
         <v>0.25129196252258312</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="14">
         <f t="shared" si="0"/>
         <v>0.21217682475288965</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="13" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17.5" thickBot="1">
-      <c r="D10" s="28">
+      <c r="D10" s="22">
         <v>2018</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28">
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22">
         <v>2021</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.5" thickBot="1">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="23">
         <v>1158.8</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="23">
         <v>1362.5</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="23">
         <v>2380.1</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="23">
         <v>3105.9</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.5" thickBot="1">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="24">
         <v>89.8</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="24">
         <v>104.5</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="24">
         <v>268.8</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="24">
         <v>294.5</v>
       </c>
     </row>
@@ -2377,19 +2377,19 @@
       <c r="B13" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="14">
         <f>D12/D11</f>
         <v>7.7493959268208498E-2</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="14">
         <f t="shared" ref="E13:G13" si="1">E12/E11</f>
         <v>7.6697247706422014E-2</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="14">
         <f t="shared" si="1"/>
         <v>0.11293643124238478</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="14">
         <f t="shared" si="1"/>
         <v>9.4819537010206373E-2</v>
       </c>
@@ -2397,5 +2397,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>